--- a/data/trans_bre/LAWTONB_2R3-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/LAWTONB_2R3-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 8,95</t>
+          <t>-8,82; 9,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 18,96</t>
+          <t>-0,7; 19,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 16,19</t>
+          <t>-3,25; 15,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 16,7</t>
+          <t>2,44; 17,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-43,32; 72,44</t>
+          <t>-41,1; 80,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 145,14</t>
+          <t>-4,52; 154,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 124,79</t>
+          <t>-15,3; 112,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 82,76</t>
+          <t>8,81; 83,71</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 15,69</t>
+          <t>-1,18; 15,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 17,53</t>
+          <t>-3,4; 17,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 17,77</t>
+          <t>0,12; 17,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,22; 17,07</t>
+          <t>4,32; 16,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 160,89</t>
+          <t>-7,47; 155,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 94,24</t>
+          <t>-11,81; 94,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 138,43</t>
+          <t>-1,6; 139,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,78; 120,59</t>
+          <t>19,54; 116,2</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 10,91</t>
+          <t>-5,66; 11,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 19,62</t>
+          <t>-3,97; 20,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 26,6</t>
+          <t>6,14; 26,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 17,82</t>
+          <t>-10,8; 18,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,18; 163,39</t>
+          <t>-40,03; 175,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 129,2</t>
+          <t>-16,46; 137,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,05; 325,96</t>
+          <t>30,81; 330,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-76,3; 216,85</t>
+          <t>-72,62; 235,56</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,06; 18,27</t>
+          <t>3,87; 18,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 8,12</t>
+          <t>-8,6; 8,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 13,56</t>
+          <t>-1,83; 13,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,6; 16,25</t>
+          <t>5,54; 16,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,48; 276,55</t>
+          <t>23,87; 313,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,8; 53,36</t>
+          <t>-35,06; 53,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 139,29</t>
+          <t>-10,31; 136,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,48; 147,31</t>
+          <t>33,59; 147,68</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 9,62</t>
+          <t>1,36; 9,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 10,99</t>
+          <t>0,31; 10,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,08; 13,05</t>
+          <t>4,51; 13,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 12,72</t>
+          <t>-5,61; 12,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,9; 91,11</t>
+          <t>9,57; 89,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 60,66</t>
+          <t>1,15; 61,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,81; 101,07</t>
+          <t>26,84; 103,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 80,65</t>
+          <t>-30,86; 80,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/LAWTONB_2R3-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/LAWTONB_2R3-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>10,54</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>43,04%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 9,94</t>
+          <t>-8,87; 9,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 19,39</t>
+          <t>-1,08; 18,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 15,34</t>
+          <t>-2,89; 14,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 17,05</t>
+          <t>3,2; 17,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,1; 80,8</t>
+          <t>-45,08; 78,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 154,35</t>
+          <t>-4,99; 143,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 112,65</t>
+          <t>-14,23; 108,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,81; 83,71</t>
+          <t>11,2; 85,04</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,29</t>
+          <t>11,73</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>66,05%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 15,29</t>
+          <t>-1,14; 15,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 17,49</t>
+          <t>-2,44; 18,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 17,58</t>
+          <t>-0,47; 16,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 16,77</t>
+          <t>5,99; 18,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 155,91</t>
+          <t>-8,21; 165,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 94,43</t>
+          <t>-8,21; 102,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 139,24</t>
+          <t>-4,63; 126,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,54; 116,2</t>
+          <t>27,54; 135,16</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>16,25</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>188,82%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 11,59</t>
+          <t>-5,64; 10,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 20,9</t>
+          <t>-5,73; 19,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 26,63</t>
+          <t>5,08; 25,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 18,55</t>
+          <t>9,45; 22,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 175,8</t>
+          <t>-40,35; 153,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 137,99</t>
+          <t>-19,91; 136,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,81; 330,23</t>
+          <t>30,41; 322,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-72,62; 235,56</t>
+          <t>75,65; 386,02</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,94</t>
+          <t>11,99</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>89,16%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 18,8</t>
+          <t>3,16; 18,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 8,18</t>
+          <t>-9,13; 7,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 13,33</t>
+          <t>-1,85; 12,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,54; 16,38</t>
+          <t>6,27; 17,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,87; 313,99</t>
+          <t>21,64; 278,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,06; 53,71</t>
+          <t>-35,41; 52,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 136,26</t>
+          <t>-12,41; 127,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,59; 147,68</t>
+          <t>37,69; 167,26</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>12,45</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>77,85%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 9,7</t>
+          <t>1,27; 9,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 10,92</t>
+          <t>0,54; 10,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 13,28</t>
+          <t>4,1; 13,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 12,89</t>
+          <t>9,19; 15,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,57; 89,44</t>
+          <t>6,46; 91,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 61,16</t>
+          <t>2,4; 57,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,84; 103,38</t>
+          <t>23,98; 99,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 80,78</t>
+          <t>49,22; 111,34</t>
         </is>
       </c>
     </row>
